--- a/data/trans_camb/MCS12_SP_R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población en el primer cuartil de la puntuación del componente de salud mental (SF12)</t>
+          <t>Población en el primer cuartil (48.388) de la puntuación del componente de salud mental (SF12)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,99; 21,96</t>
+          <t>7,73; 22,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,65; 20,87</t>
+          <t>6,86; 21,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,34; -5,53</t>
+          <t>-16,54; -5,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,74; 35,93</t>
+          <t>18,49; 35,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,85; 25,94</t>
+          <t>10,49; 26,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-25,02; -12,44</t>
+          <t>-24,74; -12,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,82; 27,04</t>
+          <t>15,88; 26,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,07; 21,7</t>
+          <t>10,63; 21,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,6; -10,97</t>
+          <t>-18,67; -10,7</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 162,11</t>
+          <t>36,2; 159,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,35; 150,36</t>
+          <t>33,2; 155,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-77,45; -39,54</t>
+          <t>-76,98; -36,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>65,37; 167,35</t>
+          <t>59,92; 167,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,47; 119,28</t>
+          <t>31,34; 117,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,5; -58,37</t>
+          <t>-81,37; -58,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,61; 144,25</t>
+          <t>64,7; 143,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,17; 116,03</t>
+          <t>41,37; 112,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-77,37; -56,82</t>
+          <t>-76,71; -56,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,33; -5,56</t>
+          <t>-16,55; -6,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-23,18; -13,51</t>
+          <t>-22,9; -13,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,18; -5,19</t>
+          <t>-16,92; -5,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,7; -9,22</t>
+          <t>-20,94; -9,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,77; -20,19</t>
+          <t>-30,66; -19,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-22,0; -10,98</t>
+          <t>-21,52; -11,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,42; -9,35</t>
+          <t>-16,66; -9,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,42; -18,16</t>
+          <t>-25,34; -18,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,9; -9,67</t>
+          <t>-17,62; -9,91</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-55,85; -22,42</t>
+          <t>-57,06; -26,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,78; -55,97</t>
+          <t>-77,05; -56,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-55,37; -21,23</t>
+          <t>-57,74; -24,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,56; -24,27</t>
+          <t>-48,19; -25,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -52,43</t>
+          <t>-70,23; -51,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,47; -28,8</t>
+          <t>-49,47; -29,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-48,95; -29,29</t>
+          <t>-46,97; -28,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,38; -56,66</t>
+          <t>-70,99; -57,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,81; -30,95</t>
+          <t>-49,75; -31,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 16,68</t>
+          <t>6,94; 15,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 10,02</t>
+          <t>2,53; 9,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,47; 13,52</t>
+          <t>5,45; 13,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,85; 19,14</t>
+          <t>7,59; 18,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 9,57</t>
+          <t>-0,5; 9,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,69; 14,0</t>
+          <t>5,25; 14,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,73; 16,22</t>
+          <t>8,72; 15,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,54; 8,71</t>
+          <t>2,12; 8,31</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 13,22</t>
+          <t>6,6; 12,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>121,73; 759,12</t>
+          <t>123,32; 699,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37,97; 420,19</t>
+          <t>39,84; 447,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>96,8; 639,31</t>
+          <t>93,39; 650,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61,44; 238,02</t>
+          <t>61,22; 239,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 117,93</t>
+          <t>-4,11; 115,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>36,1; 181,34</t>
+          <t>41,03; 195,04</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>102,02; 291,06</t>
+          <t>104,36; 293,27</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>29,37; 156,84</t>
+          <t>23,96; 145,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74,82; 235,92</t>
+          <t>75,83; 231,51</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,33; 18,28</t>
+          <t>7,18; 17,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,31; 14,79</t>
+          <t>4,12; 14,25</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 7,92</t>
+          <t>-2,52; 8,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,82; 32,44</t>
+          <t>19,3; 31,7</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,95; 21,54</t>
+          <t>9,4; 22,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 6,88</t>
+          <t>-6,88; 6,93</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,14; 23,63</t>
+          <t>14,76; 23,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,57; 17,08</t>
+          <t>8,02; 16,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 6,27</t>
+          <t>-3,14; 6,5</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>59,58; 245,24</t>
+          <t>56,52; 230,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,25; 186,63</t>
+          <t>29,69; 180,75</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 101,54</t>
+          <t>-22,63; 102,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>98,99; 230,88</t>
+          <t>97,19; 233,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,4; 152,53</t>
+          <t>45,06; 160,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-39,15; 46,48</t>
+          <t>-36,45; 46,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,35; 201,67</t>
+          <t>98,86; 208,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>58,64; 152,4</t>
+          <t>52,83; 144,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 52,83</t>
+          <t>-21,34; 55,0</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,62; -9,74</t>
+          <t>-25,18; -9,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,32; 20,21</t>
+          <t>1,41; 20,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 26,1</t>
+          <t>8,98; 27,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 3,24</t>
+          <t>-16,45; 3,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 22,78</t>
+          <t>3,27; 22,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,18; 30,24</t>
+          <t>13,67; 29,71</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-17,48; -5,21</t>
+          <t>-18,0; -5,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,9; 17,61</t>
+          <t>5,14; 18,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,25; 26,19</t>
+          <t>13,8; 26,19</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,68; -33,55</t>
+          <t>-71,48; -36,11</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3,99; 80,84</t>
+          <t>4,47; 80,63</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24,15; 101,02</t>
+          <t>23,93; 110,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-36,25; 8,99</t>
+          <t>-38,49; 9,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>6,38; 68,96</t>
+          <t>7,56; 69,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,94; 94,42</t>
+          <t>30,81; 93,1</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-47,25; -17,15</t>
+          <t>-48,62; -18,58</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13,7; 57,04</t>
+          <t>13,16; 58,62</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>37,46; 85,78</t>
+          <t>35,83; 86,41</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,8; 16,83</t>
+          <t>6,18; 16,71</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,45; 12,01</t>
+          <t>2,43; 12,4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,82</t>
+          <t>6,3; 15,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,25; 18,2</t>
+          <t>3,79; 17,15</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,19; 15,29</t>
+          <t>2,15; 15,39</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 10,77</t>
+          <t>-0,46; 10,25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,48; 15,24</t>
+          <t>6,58; 15,29</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,07; 11,73</t>
+          <t>3,67; 11,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4,23; 11,45</t>
+          <t>3,99; 11,49</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>68,33; 480,54</t>
+          <t>76,9; 476,83</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23,17; 331,84</t>
+          <t>29,04; 371,05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>78,72; 453,95</t>
+          <t>79,9; 484,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>24,31; 153,75</t>
+          <t>21,26; 152,45</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11,34; 132,95</t>
+          <t>9,37; 128,77</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 92,88</t>
+          <t>-2,86; 85,51</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>52,22; 180,03</t>
+          <t>54,35; 181,65</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>27,11; 144,78</t>
+          <t>28,78; 143,43</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>34,66; 138,3</t>
+          <t>30,12; 137,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,8; 9,03</t>
+          <t>0,29; 8,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,87</t>
+          <t>1,9; 11,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7,54; 18,44</t>
+          <t>6,96; 18,1</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 8,51</t>
+          <t>-0,75; 8,22</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,78; 14,61</t>
+          <t>5,36; 14,28</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>14,7; 60,82</t>
+          <t>15,3; 59,13</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,46</t>
+          <t>1,09; 7,47</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,87; 11,41</t>
+          <t>4,93; 11,59</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,45; 48,09</t>
+          <t>13,7; 50,3</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5,0; 77,2</t>
+          <t>1,57; 73,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>14,73; 89,67</t>
+          <t>10,88; 95,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>43,21; 149,68</t>
+          <t>41,9; 147,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 48,15</t>
+          <t>-4,52; 44,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,98; 84,69</t>
+          <t>23,98; 80,5</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>70,64; 338,35</t>
+          <t>72,96; 316,45</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,15; 47,37</t>
+          <t>5,9; 47,42</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>26,13; 72,09</t>
+          <t>25,89; 74,91</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>75,06; 287,03</t>
+          <t>77,25; 319,66</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 8,56</t>
+          <t>-1,19; 8,63</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-15,24; -6,56</t>
+          <t>-14,98; -6,35</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-22,27; -5,56</t>
+          <t>-25,28; -5,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 8,68</t>
+          <t>-1,48; 8,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,67; -8,57</t>
+          <t>-17,66; -8,28</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,04; -0,61</t>
+          <t>-10,0; -0,5</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,41; 7,23</t>
+          <t>-0,19; 6,98</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-14,94; -8,8</t>
+          <t>-15,13; -8,81</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-19,54; -5,03</t>
+          <t>-20,11; -5,17</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 31,01</t>
+          <t>-3,71; 31,5</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-47,53; -24,05</t>
+          <t>-46,92; -22,81</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,34; -19,85</t>
+          <t>-74,93; -19,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 26,07</t>
+          <t>-3,7; 25,65</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-46,16; -25,4</t>
+          <t>-46,8; -25,79</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-26,16; -2,1</t>
+          <t>-26,04; -1,63</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>1,2; 23,01</t>
+          <t>-0,57; 22,49</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-43,41; -28,28</t>
+          <t>-43,38; -27,5</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-56,33; -15,87</t>
+          <t>-59,45; -16,29</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,63</t>
+          <t>1,68; 5,75</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 2,2</t>
+          <t>-1,66; 2,25</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 2,07</t>
+          <t>-5,14; 2,21</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,51</t>
+          <t>3,86; 8,42</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,46</t>
+          <t>-1,8; 2,43</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 17,54</t>
+          <t>-0,4; 18,28</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,43</t>
+          <t>3,38; 6,37</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,66</t>
+          <t>-1,27; 1,61</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 9,47</t>
+          <t>-1,02; 10,09</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>7,09; 31,83</t>
+          <t>8,72; 32,61</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 12,62</t>
+          <t>-8,52; 12,76</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-23,33; 11,61</t>
+          <t>-26,14; 12,46</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13,78; 33,52</t>
+          <t>13,92; 32,96</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,27; 9,84</t>
+          <t>-6,51; 9,52</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 71,67</t>
+          <t>-1,51; 72,14</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,31; 29,76</t>
+          <t>14,34; 29,08</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 7,66</t>
+          <t>-5,38; 7,45</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 42,23</t>
+          <t>-4,51; 45,74</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/MCS12_SP_R3-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/MCS12_SP_R3-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-10,96</t>
+          <t>-11,55</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-18,42</t>
+          <t>-18,86</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-14,61</t>
+          <t>-15,12</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,73; 22,12</t>
+          <t>7,77; 22,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 21,3</t>
+          <t>6,75; 21,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,54; -5,61</t>
+          <t>-16,84; -6,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,49; 35,63</t>
+          <t>19,21; 35,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,49; 26,23</t>
+          <t>9,21; 26,11</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-24,74; -12,74</t>
+          <t>-24,6; -13,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,88; 26,84</t>
+          <t>15,71; 26,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,63; 21,42</t>
+          <t>10,64; 21,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-18,67; -10,7</t>
+          <t>-19,55; -11,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-62,37%</t>
+          <t>-65,75%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-71,73%</t>
+          <t>-73,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-67,84%</t>
+          <t>-70,21%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>36,2; 159,22</t>
+          <t>33,07; 155,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,2; 155,35</t>
+          <t>31,75; 146,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-76,98; -36,76</t>
+          <t>-79,46; -45,37</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59,92; 167,98</t>
+          <t>63,73; 164,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,34; 117,1</t>
+          <t>30,24; 122,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,37; -58,84</t>
+          <t>-81,54; -61,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,7; 143,56</t>
+          <t>62,91; 142,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>41,37; 112,89</t>
+          <t>43,28; 112,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-76,71; -56,61</t>
+          <t>-78,07; -60,28</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,99</t>
+          <t>-10,73</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-16,67</t>
+          <t>-16,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-13,92</t>
+          <t>-13,69</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -6,24</t>
+          <t>-16,98; -6,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-22,9; -13,23</t>
+          <t>-22,97; -13,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-16,92; -5,58</t>
+          <t>-16,44; -5,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -9,3</t>
+          <t>-21,22; -8,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,66; -19,61</t>
+          <t>-31,34; -19,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-21,52; -11,08</t>
+          <t>-22,2; -11,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-16,66; -9,02</t>
+          <t>-17,0; -8,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,34; -18,39</t>
+          <t>-25,55; -18,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,62; -9,91</t>
+          <t>-17,38; -9,68</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-41,31%</t>
+          <t>-40,33%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-40,81%</t>
+          <t>-40,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-41,19%</t>
+          <t>-40,51%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,06; -26,36</t>
+          <t>-57,33; -25,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-77,05; -56,05</t>
+          <t>-76,56; -56,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-57,74; -24,37</t>
+          <t>-55,43; -20,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,19; -25,07</t>
+          <t>-48,55; -23,4</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,23; -51,96</t>
+          <t>-71,02; -52,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,47; -29,02</t>
+          <t>-50,22; -29,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,97; -28,6</t>
+          <t>-47,68; -28,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-70,99; -57,56</t>
+          <t>-70,56; -57,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-49,75; -31,65</t>
+          <t>-49,5; -30,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>10,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,64</t>
+          <t>9,96</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,61</t>
+          <t>10,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 15,81</t>
+          <t>7,42; 16,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 9,81</t>
+          <t>2,37; 10,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 13,98</t>
+          <t>6,17; 14,93</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,59; 18,94</t>
+          <t>8,13; 19,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 9,43</t>
+          <t>-0,56; 9,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,25; 14,6</t>
+          <t>4,99; 14,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,72; 15,96</t>
+          <t>9,08; 16,1</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 8,31</t>
+          <t>2,26; 8,72</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,6; 12,77</t>
+          <t>7,44; 13,58</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>261,3%</t>
+          <t>286,47%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>137,86%</t>
+          <t>146,94%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123,32; 699,67</t>
+          <t>136,18; 835,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>39,84; 447,58</t>
+          <t>36,39; 462,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93,39; 650,87</t>
+          <t>103,62; 751,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61,22; 239,17</t>
+          <t>61,48; 243,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 115,88</t>
+          <t>-5,46; 123,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>41,03; 195,04</t>
+          <t>39,19; 183,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>104,36; 293,27</t>
+          <t>102,62; 295,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>23,96; 145,08</t>
+          <t>27,06; 160,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75,83; 231,51</t>
+          <t>85,78; 244,12</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,61</t>
+          <t>3,24</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66</t>
+          <t>5,12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,09</t>
+          <t>4,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>7,18; 17,69</t>
+          <t>6,73; 17,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,12; 14,25</t>
+          <t>4,29; 14,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 8,04</t>
+          <t>-1,83; 8,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,3; 31,7</t>
+          <t>19,24; 31,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,4; 22,37</t>
+          <t>9,53; 21,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,88; 6,93</t>
+          <t>-0,62; 10,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,76; 23,44</t>
+          <t>15,19; 23,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,02; 16,77</t>
+          <t>8,35; 16,53</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 6,5</t>
+          <t>0,47; 7,95</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>30,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>56,52; 230,82</t>
+          <t>54,27; 238,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29,69; 180,75</t>
+          <t>34,83; 194,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 102,46</t>
+          <t>-15,55; 108,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>97,19; 233,37</t>
+          <t>98,54; 233,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,06; 160,12</t>
+          <t>50,5; 153,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 46,33</t>
+          <t>-3,69; 76,1</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>98,86; 208,11</t>
+          <t>95,95; 198,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>52,83; 144,86</t>
+          <t>55,22; 142,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-21,34; 55,0</t>
+          <t>2,69; 69,14</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17,97</t>
+          <t>17,17</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,93</t>
+          <t>20,91</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20,33</t>
+          <t>19,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,18; -9,61</t>
+          <t>-25,12; -9,44</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,41; 20,17</t>
+          <t>1,97; 19,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,98; 27,22</t>
+          <t>8,7; 26,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,45; 3,17</t>
+          <t>-15,86; 2,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,27; 22,65</t>
+          <t>3,66; 21,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>13,67; 29,71</t>
+          <t>12,01; 28,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-18,0; -5,85</t>
+          <t>-17,44; -5,28</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 18,41</t>
+          <t>4,61; 18,01</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13,8; 26,19</t>
+          <t>12,87; 25,02</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>56,36%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>59,28%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,48; -36,11</t>
+          <t>-72,74; -36,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,47; 80,63</t>
+          <t>5,84; 77,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23,93; 110,47</t>
+          <t>23,68; 103,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-38,49; 9,9</t>
+          <t>-37,52; 7,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,56; 69,71</t>
+          <t>8,38; 65,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,81; 93,1</t>
+          <t>26,56; 86,84</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,62; -18,58</t>
+          <t>-47,14; -17,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>13,16; 58,62</t>
+          <t>12,11; 58,42</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35,83; 86,41</t>
+          <t>33,79; 82,97</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10,95</t>
+          <t>10,35</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>5,14</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>7,66</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>6,18; 16,71</t>
+          <t>6,56; 16,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,43; 12,4</t>
+          <t>2,62; 11,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6,3; 15,68</t>
+          <t>6,34; 15,05</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,79; 17,15</t>
+          <t>3,72; 17,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>2,15; 15,39</t>
+          <t>1,61; 15,37</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 10,25</t>
+          <t>0,09; 10,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,58; 15,29</t>
+          <t>6,79; 15,46</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>3,67; 11,85</t>
+          <t>3,56; 12,44</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,99; 11,49</t>
+          <t>3,91; 11,17</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>211,48%</t>
+          <t>200,02%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76,9; 476,83</t>
+          <t>91,84; 479,78</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>29,04; 371,05</t>
+          <t>35,21; 360,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>79,9; 484,62</t>
+          <t>86,27; 450,42</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>21,26; 152,45</t>
+          <t>15,28; 137,56</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>9,37; 128,77</t>
+          <t>7,74; 124,25</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 85,51</t>
+          <t>-0,04; 91,22</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>54,35; 181,65</t>
+          <t>55,67; 182,16</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>28,78; 143,43</t>
+          <t>27,71; 143,09</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>30,12; 137,16</t>
+          <t>33,38; 133,76</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12,86</t>
+          <t>11,2</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,89</t>
+          <t>17,06</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>24,26</t>
+          <t>14,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,29; 8,9</t>
+          <t>0,42; 8,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,9; 11,37</t>
+          <t>2,11; 11,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>6,96; 18,1</t>
+          <t>6,36; 15,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 8,22</t>
+          <t>-1,44; 8,21</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>5,36; 14,28</t>
+          <t>4,69; 14,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,3; 59,13</t>
+          <t>12,22; 21,61</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>1,09; 7,47</t>
+          <t>0,91; 7,46</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,59</t>
+          <t>4,67; 11,47</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>13,7; 50,3</t>
+          <t>10,88; 17,21</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>158,59%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>141,02%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>1,57; 73,94</t>
+          <t>2,57; 74,86</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>10,88; 95,82</t>
+          <t>12,45; 88,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>41,9; 147,91</t>
+          <t>40,2; 133,76</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 44,57</t>
+          <t>-6,47; 46,96</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>23,98; 80,5</t>
+          <t>21,39; 81,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>72,96; 316,45</t>
+          <t>53,12; 119,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,9; 47,42</t>
+          <t>5,17; 47,02</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>25,89; 74,91</t>
+          <t>25,65; 74,44</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>77,25; 319,66</t>
+          <t>57,63; 110,47</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-13,13</t>
+          <t>-7,8</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-5,51</t>
+          <t>-6,07</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-10,27</t>
+          <t>-6,94</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 8,63</t>
+          <t>-1,33; 8,82</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -6,35</t>
+          <t>-15,25; -6,45</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-25,28; -5,58</t>
+          <t>-12,5; -3,49</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 8,69</t>
+          <t>-1,72; 8,32</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -8,28</t>
+          <t>-18,01; -8,38</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-10,0; -0,5</t>
+          <t>-11,05; -1,6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 6,98</t>
+          <t>0,19; 6,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-15,13; -8,81</t>
+          <t>-15,22; -8,71</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-20,11; -5,17</t>
+          <t>-10,16; -3,87</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-44,08%</t>
+          <t>-26,2%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-15,41%</t>
+          <t>-17,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-31,28%</t>
+          <t>-21,14%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 31,5</t>
+          <t>-3,99; 31,9</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-46,92; -22,81</t>
+          <t>-47,6; -23,61</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-74,93; -19,49</t>
+          <t>-38,45; -12,59</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 25,65</t>
+          <t>-4,66; 25,45</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-46,8; -25,79</t>
+          <t>-47,06; -25,11</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-26,04; -1,63</t>
+          <t>-28,19; -4,73</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 22,49</t>
+          <t>0,61; 21,48</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-43,38; -27,5</t>
+          <t>-44,05; -27,58</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-59,45; -16,29</t>
+          <t>-29,31; -12,6</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>1,02</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>1,17</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,75</t>
+          <t>1,66; 6,01</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 2,25</t>
+          <t>-1,55; 2,23</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 2,21</t>
+          <t>-1,25; 2,92</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,42</t>
+          <t>3,96; 8,39</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 2,43</t>
+          <t>-1,91; 2,47</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 18,28</t>
+          <t>-0,8; 3,19</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,37</t>
+          <t>3,36; 6,36</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,61</t>
+          <t>-1,29; 1,66</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 10,09</t>
+          <t>-0,14; 2,65</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-1,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>8,72; 32,61</t>
+          <t>8,57; 33,9</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-8,52; 12,76</t>
+          <t>-7,85; 12,79</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-26,14; 12,46</t>
+          <t>-6,24; 16,8</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>13,92; 32,96</t>
+          <t>14,14; 32,89</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-6,51; 9,52</t>
+          <t>-6,84; 9,75</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 72,14</t>
+          <t>-3,01; 12,41</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,34; 29,08</t>
+          <t>14,25; 28,71</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 7,45</t>
+          <t>-5,5; 7,57</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 45,74</t>
+          <t>-0,61; 12,15</t>
         </is>
       </c>
     </row>
